--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_OV.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_OV.xlsx
@@ -428,7 +428,7 @@
         <v>238.3325959221063</v>
       </c>
       <c r="E4">
-        <v>278.5819762149916</v>
+        <v>278.5819762149917</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -530,7 +530,7 @@
         <v>96.32679321237634</v>
       </c>
       <c r="E10">
-        <v>117.9515045051195</v>
+        <v>117.9515045051196</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -547,7 +547,7 @@
         <v>14.82492533592836</v>
       </c>
       <c r="E11">
-        <v>20.02365319544392</v>
+        <v>20.02365319544393</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -564,7 +564,7 @@
         <v>17.21152648281952</v>
       </c>
       <c r="E12">
-        <v>25.85951846136574</v>
+        <v>25.85951846136575</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -581,7 +581,7 @@
         <v>45.36757355848336</v>
       </c>
       <c r="E13">
-        <v>58.81711301674312</v>
+        <v>58.81711301674314</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_OV.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_OV.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>195.6369514302971</v>
+        <v>7.48849574852812</v>
       </c>
       <c r="C2">
-        <v>274.5212523286614</v>
+        <v>22.32947985448442</v>
       </c>
       <c r="D2">
-        <v>310.9164639157244</v>
+        <v>49.09207324985122</v>
       </c>
       <c r="E2">
-        <v>331.6980579585959</v>
+        <v>79.73511008620095</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>212.3020318638763</v>
+        <v>71.05619025648105</v>
       </c>
       <c r="C3">
-        <v>301.5199409104664</v>
+        <v>186.3050041398004</v>
       </c>
       <c r="D3">
-        <v>345.0360427527871</v>
+        <v>259.1291096592361</v>
       </c>
       <c r="E3">
-        <v>376.8132310762155</v>
+        <v>314.0110258968462</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>123.7288461065254</v>
+        <v>4.698563776197166</v>
       </c>
       <c r="C4">
-        <v>184.5666901096577</v>
+        <v>13.1833350078327</v>
       </c>
       <c r="D4">
-        <v>238.3325959221063</v>
+        <v>27.15181472530326</v>
       </c>
       <c r="E4">
-        <v>278.5819762149917</v>
+        <v>40.96793767867525</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>61.40334605318127</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>72.80949010845977</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>70.94443891571204</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>66.50496848381502</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>44.04257576097817</v>
+        <v>14.78352193375491</v>
       </c>
       <c r="C6">
-        <v>46.77444963526305</v>
+        <v>19.95273725700033</v>
       </c>
       <c r="D6">
-        <v>42.76563506891137</v>
+        <v>16.74738156544781</v>
       </c>
       <c r="E6">
-        <v>35.66040263999618</v>
+        <v>11.55196141859031</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>5.159099170148625</v>
+        <v>1.719699723382875</v>
       </c>
       <c r="C7">
-        <v>6.020632359621939</v>
+        <v>4.013754906414626</v>
       </c>
       <c r="D7">
-        <v>6.259680405911465</v>
+        <v>4.590432297668407</v>
       </c>
       <c r="E7">
-        <v>5.742853052019696</v>
+        <v>4.594282441615757</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>164.6838116579072</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>239.2049769897744</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>255.8256801261424</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>258.7641707967055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>122.6010930740759</v>
+        <v>220.2058467835345</v>
       </c>
       <c r="C9">
-        <v>142.4294578933071</v>
+        <v>408.0225532885561</v>
       </c>
       <c r="D9">
-        <v>121.1886443030973</v>
+        <v>471.8121006363303</v>
       </c>
       <c r="E9">
-        <v>101.5825505989881</v>
+        <v>485.8295898212476</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>42.29312015485393</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>68.28392278590431</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>96.32679321237634</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>117.9515045051196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>6.837861144587681</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>10.34375488317571</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>14.82492533592836</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>20.02365319544393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>4.116260849524891</v>
+        <v>50.55612684416468</v>
       </c>
       <c r="C12">
-        <v>7.939078693490086</v>
+        <v>105.9867005580927</v>
       </c>
       <c r="D12">
-        <v>17.21152648281952</v>
+        <v>194.4902492558606</v>
       </c>
       <c r="E12">
-        <v>25.85951846136575</v>
+        <v>225.4419558170347</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>18.19500273404358</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>29.58635330221794</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>45.36757355848336</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>58.81711301674314</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_OV.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_OV.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>7.48849574852812</v>
+        <v>25.30394102331987</v>
       </c>
       <c r="C2">
-        <v>22.32947985448442</v>
+        <v>35.50694042095262</v>
       </c>
       <c r="D2">
-        <v>49.09207324985122</v>
+        <v>40.21434503341107</v>
       </c>
       <c r="E2">
-        <v>79.73511008620095</v>
+        <v>42.9022637838663</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>71.05619025648105</v>
+        <v>134.6885599299338</v>
       </c>
       <c r="C3">
-        <v>186.3050041398004</v>
+        <v>191.2901458118336</v>
       </c>
       <c r="D3">
-        <v>259.1291096592361</v>
+        <v>218.897611644589</v>
       </c>
       <c r="E3">
-        <v>314.0110258968462</v>
+        <v>239.0576812224869</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>4.698563776197166</v>
+        <v>11.4611983761834</v>
       </c>
       <c r="C4">
-        <v>13.1833350078327</v>
+        <v>17.09670392594725</v>
       </c>
       <c r="D4">
-        <v>27.15181472530326</v>
+        <v>22.07712467488985</v>
       </c>
       <c r="E4">
-        <v>40.96793767867525</v>
+        <v>25.80548832307291</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>14.78352193375491</v>
+        <v>16.2749272952126</v>
       </c>
       <c r="C6">
-        <v>19.95273725700033</v>
+        <v>17.28442884945798</v>
       </c>
       <c r="D6">
-        <v>16.74738156544781</v>
+        <v>15.80306304648039</v>
       </c>
       <c r="E6">
-        <v>11.55196141859031</v>
+        <v>13.17748678991103</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1.719699723382875</v>
+        <v>3.267429474427463</v>
       </c>
       <c r="C7">
-        <v>4.013754906414626</v>
+        <v>3.813067161093896</v>
       </c>
       <c r="D7">
-        <v>4.590432297668407</v>
+        <v>3.964464257077259</v>
       </c>
       <c r="E7">
-        <v>4.594282441615757</v>
+        <v>3.637140266279141</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>220.2058467835345</v>
+        <v>408.9176893693453</v>
       </c>
       <c r="C9">
-        <v>408.0225532885561</v>
+        <v>475.0522475739238</v>
       </c>
       <c r="D9">
-        <v>471.8121006363303</v>
+        <v>404.2066768220738</v>
       </c>
       <c r="E9">
-        <v>485.8295898212476</v>
+        <v>338.8134708235016</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>50.55612684416468</v>
+        <v>47.02437236324322</v>
       </c>
       <c r="C12">
-        <v>105.9867005580927</v>
+        <v>90.69643697309877</v>
       </c>
       <c r="D12">
-        <v>194.4902492558606</v>
+        <v>196.6253500094255</v>
       </c>
       <c r="E12">
-        <v>225.4419558170347</v>
+        <v>295.4204482453491</v>
       </c>
     </row>
     <row r="13" spans="1:5">
